--- a/rbda-kiosk/du_lieu_test/TEST_03_xep_hang_nguyen_vong.xlsx
+++ b/rbda-kiosk/du_lieu_test/TEST_03_xep_hang_nguyen_vong.xlsx
@@ -441,7 +441,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -508,16 +508,8 @@
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -543,17 +535,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -576,24 +568,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -610,25 +594,29 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -644,15 +632,19 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -670,7 +662,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -678,7 +670,11 @@
           <t>clb_tienganh</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -696,7 +692,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -704,9 +700,21 @@
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -722,12 +730,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -752,24 +760,20 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_vanhoc</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -786,29 +790,25 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -824,17 +824,17 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_vanhoc</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -854,16 +854,24 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -885,17 +893,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -918,21 +926,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_bongro</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -948,19 +964,15 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -978,22 +990,22 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1012,16 +1024,24 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1038,24 +1058,16 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1072,17 +1084,17 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1102,15 +1114,19 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_robotics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1132,17 +1148,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1171,14 +1187,10 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1200,19 +1212,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1234,7 +1242,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1242,16 +1250,8 @@
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1268,17 +1268,29 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>clb_khoahoc</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1294,19 +1306,15 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1324,12 +1332,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1355,19 +1363,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_bongro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1384,7 +1388,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1392,9 +1396,21 @@
           <t>clb_tinhoc</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1410,20 +1426,24 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tinhnguyen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1440,7 +1460,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1448,7 +1468,11 @@
           <t>clb_tinhoc</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1466,29 +1490,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1504,20 +1516,24 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1534,20 +1550,24 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1569,10 +1589,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1594,7 +1618,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1604,11 +1628,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1624,19 +1656,15 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1659,22 +1687,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_khoahoc</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_bongda</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1720,12 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_bongro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1705,11 +1733,7 @@
           <t>clb_tinhoc</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1726,17 +1750,17 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -1756,16 +1780,24 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_bongro</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1782,21 +1814,29 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>clb_bongda</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1812,7 +1852,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_bongro</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1838,16 +1878,24 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1864,29 +1912,25 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1902,12 +1946,12 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1932,15 +1976,19 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1958,7 +2006,7 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_vanhoc</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1966,16 +2014,8 @@
           <t>clb_bongda</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1992,20 +2032,24 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_bongro</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tinhnguyen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2026,22 +2070,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2060,16 +2104,24 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2086,12 +2138,12 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2099,8 +2151,16 @@
           <t>clb_tinhoc</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2116,24 +2176,16 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_tinhnguyen</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2150,7 +2202,7 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2160,14 +2212,10 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2184,17 +2232,29 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2210,16 +2270,24 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2236,25 +2304,29 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>clb_khoahoc</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2274,24 +2346,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2312,12 +2380,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -2338,25 +2406,29 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_vanhoc</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2372,16 +2444,24 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2402,7 +2482,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2428,22 +2508,22 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -2462,29 +2542,17 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2504,7 +2572,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2514,7 +2582,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2534,12 +2602,12 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tinhnguyen</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2564,21 +2632,29 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_vanhoc</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2594,17 +2670,17 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_robotics</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_bongro</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2624,19 +2700,15 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2654,24 +2726,20 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -2693,19 +2761,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -2726,24 +2790,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -2768,8 +2828,16 @@
           <t>clb_bongda</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -2790,7 +2858,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2800,12 +2868,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -2828,29 +2896,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_khoahoc</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2866,29 +2930,17 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tinhnguyen</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2909,12 +2961,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2930,22 +2994,22 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_khoahoc</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -2964,24 +3028,16 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -2998,19 +3054,15 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3028,19 +3080,15 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3058,24 +3106,20 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -3096,29 +3140,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_khoahoc</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3134,19 +3174,15 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
-        </is>
-      </c>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3164,17 +3200,29 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>clb_bongro</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3190,17 +3238,17 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_vanhoc</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -3220,24 +3268,20 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
@@ -3254,16 +3298,24 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>clb_robotics</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
@@ -3285,19 +3337,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -3314,7 +3362,7 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3322,7 +3370,11 @@
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3340,24 +3392,20 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
@@ -3374,25 +3422,29 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
           <t>clb_robotics</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3412,17 +3464,29 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>clb_amnhac</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3443,12 +3507,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -3468,17 +3532,17 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3486,11 +3550,7 @@
           <t>clb_vanhoc</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3510,19 +3570,15 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>clb_bongda</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3540,17 +3596,17 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_bongro</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -3570,24 +3626,16 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
@@ -3604,15 +3652,19 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3639,24 +3691,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3676,17 +3716,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -3706,19 +3746,15 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3740,12 +3776,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -3766,24 +3802,16 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3800,19 +3828,15 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_bongro</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3830,17 +3854,17 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>clb_vanhoc</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>clb_tinhnguyen</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -3860,16 +3884,24 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
@@ -3886,15 +3918,19 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3916,24 +3952,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
@@ -3950,21 +3982,29 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3985,24 +4025,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>clb_vanhoc</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>clb_mythuat</t>
-        </is>
-      </c>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4018,12 +4046,12 @@
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4031,8 +4059,16 @@
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4048,21 +4084,29 @@
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>clb_amnhac</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4078,15 +4122,19 @@
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>clb_khoahoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
+          <t>clb_bongda</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4104,7 +4152,7 @@
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4114,14 +4162,10 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>clb_tienganh</t>
-        </is>
-      </c>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
@@ -4138,24 +4182,20 @@
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>clb_mythuat</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>clb_khoahoc</t>
-        </is>
-      </c>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
@@ -4176,25 +4216,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>clb_tienganh</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>clb_vanhoc</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_amnhac</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>clb_tinhnguyen</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>clb_tienganh</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4210,19 +4254,15 @@
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>clb_bongda</t>
-        </is>
-      </c>
+          <t>clb_bongro</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4240,16 +4280,24 @@
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>clb_tinhoc</t>
+          <t>clb_bongda</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>clb_amnhac</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+          <t>clb_tinhoc</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>clb_robotics</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>clb_mythuat</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
@@ -4270,17 +4318,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>clb_tinhnguyen</t>
+          <t>clb_tinhoc</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>clb_robotics</t>
+          <t>clb_mythuat</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>clb_bongro</t>
+          <t>clb_tienganh</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -4297,7 +4345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="82" customWidth="1" min="1" max="1"/>
@@ -4333,36 +4381,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nguyện vọng chủ yếu nằm trong số CLB em đã đăng ký thi. Khoảng</t>
+          <t>Nhu cầu CỐ Ý dồn vào vài CLB: Bóng đá, Tin học và Mỹ thuật đông</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1/4 số em có thêm một nguyện vọng vào CLB chưa thi — vẫn hợp lệ,</t>
+          <t>gấp nhiều lần chỉ tiêu, còn Khoa học, Văn học và Tình nguyện thì</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vì học sinh không thi vẫn được xét vào CLB đó.</t>
+          <t>gần như không ai chọn. Nhờ vậy mới thấy thuật toán phải làm việc:</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>nhiều em trượt xuống nguyện vọng 2-3, và suất dự trữ thực sự</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>quyết định ai vào ai không.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Sinh bằng du_lieu_test/tao_du_lieu_test.py, seed = 2026</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Chạy lại script luôn cho ra đúng bộ dữ liệu này.</t>
         </is>
